--- a/outputs/system-test-cases/点巡检系统测试用例.xlsx
+++ b/outputs/system-test-cases/点巡检系统测试用例.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R9e3408a438e141b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能用例" sheetId="2" r:id="R08ddffee9ee046b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="百数云入口检查清单" sheetId="3" r:id="R8a0c7a37691e4cf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API与数据校验" sheetId="4" r:id="Rbfc6414fbc46485e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与回归" sheetId="5" r:id="R76de1f480ea4476c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试数据准备" sheetId="6" r:id="Rafe150eed3c34f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="Rf6364159849a46a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能用例" sheetId="2" r:id="Rcc0bb9d2761441d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="百数云入口检查清单" sheetId="3" r:id="R43937c5f9323464d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API与数据校验" sheetId="4" r:id="Rfb1db86c2ea549b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与回归" sheetId="5" r:id="R26e438d5030c4819"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试数据准备" sheetId="6" r:id="R35935b8da81742b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -765,7 +765,7 @@
         </x:is>
       </x:c>
       <x:c r="B24" s="8" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D24" s="8" t="inlineStr">
         <x:is>
@@ -1270,26 +1270,36 @@
           <x:t xml:space="preserve">P0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="8" t="str">
-        <x:v>设备台账云端全量同步后列表展示字段正确</x:v>
-      </x:c>
-      <x:c r="F7" s="8" t="str">
-        <x:v>百数云设备台账中存在超过 300 条设备，且包含启用、停用、不同分类、不同点检状态设备。</x:v>
-      </x:c>
-      <x:c r="G7" s="8" t="str">
-        <x:v>1. 从百数云菜单进入设备台账页面
+      <x:c r="E7" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">设备台账云端全量同步后列表展示字段正确</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">百数云设备台账中存在超过 300 条设备，且包含启用、停用、不同分类、不同点检状态设备。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 从百数云菜单进入设备台账页面
 2. 确认页面自动同步或点击刷新/重新打开
 3. 查看左侧分类数量、列表页脚总数和分页数据
-4. 抽查 300 条以后位置的设备是否可通过分页或搜索展示</x:v>
-      </x:c>
-      <x:c r="H7" s="8" t="str">
-        <x:v>1. 页面按 data_count 总数与 data 接口 limit=300、skip 分页拉取全量设备
+4. 抽查 300 条以后位置的设备是否可通过分页或搜索展示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 页面按 data_count 总数与 data 接口 limit=300、skip 分页拉取全量设备
 2. 设备总数不被单次接口 300 条上限截断
 3. 设备编号、名称、分类、型号、状态、位置、责任人、点检状态展示正确
-4. 空数据时有空态提示</x:v>
-      </x:c>
-      <x:c r="I7" s="8" t="str">
-        <x:v>抽查 data_count 与页面总数一致；抽查 3 条设备记录，与百数云设备台账字段一致。</x:v>
+4. 空数据时有空态提示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">抽查 data_count 与页面总数一致；抽查 3 条设备记录，与百数云设备台账字段一致。</x:t>
+        </x:is>
       </x:c>
       <x:c r="J7" s="8" t="inlineStr">
         <x:is>
@@ -1442,13 +1452,11 @@
       </x:c>
       <x:c r="E10" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">新增设备必填字段、所属分类智能下拉和云端落库</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">设备类型、场地、资产类别等底表已有可选项；云端模式启用；所属分类至少有两个可选项。</x:t>
-        </x:is>
+          <x:t xml:space="preserve">新增设备必填字段、所属分类智能下拉、一级/二级车间选择和云端落库</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="8" t="str">
+        <x:v>设备类型、场地、资产类别等底表已有可选项；云端模式启用；所属分类至少有两个可选项；场地底表包含一级区域及其下级场地/部门，二级存在可校验的“一级-二级”展示样例。</x:v>
       </x:c>
       <x:c r="G10" s="8" t="inlineStr">
         <x:is>
@@ -1458,26 +1466,26 @@
 4. 仅剩唯一匹配项时按回车选中
 5. 再次展开后按 ESC 或点击外部关闭
 6. hover 已选中值并点击右侧 × 清空，再重新选择分类和设备类型
-7. 填写设备名称、厂内编号、型号、车间、区域等
-8. 保存</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 未选中时显示灰色虚的“请选择”，.ss-display 本身为空
+7. 展开所属车间，先选择一级车间/区域，观察区域字段联动
+8. 再展开所属车间，选择同一一级下的二级场地/部门，观察区域字段联动
+9. 填写设备名称、厂内编号、型号、资产类别、状态等
+10. 保存</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" s="8" t="str">
+        <x:v>1. 未选中时显示灰色虚的“请选择”，.ss-display 本身为空
 2. 点击后下拉展开，输入框获得焦点并可直接打字
 3. 不匹配项隐藏，匹配项可点击选择并触发 change，设备类型联动刷新
 4. 唯一匹配项按回车后自动选中并关闭
 5. ESC 或点击外部关闭下拉并恢复显示
 6. 清空后触发 change 并恢复占位符
-7. 必填项通过后保存成功，弹窗关闭，列表出现新设备
-8. 云端设备台账新增对应记录</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">核对设备名称、分类、类型、车间、区域、状态、入厂日期、二维码相关字段；回归所属分类智能下拉只影响该字段，其它下拉保持原交互。</x:t>
-        </x:is>
+7. 所属车间下拉按一级、二级原层级展示，一级节点在层级中直接可选，不重复单独展示同名一级选项，选项文字不显示场地编号
+8. 选择一级时区域字段自动带入同名一级区域；选择二级时显示值/保存值为“一级-二级”（如“铸造车间-二车间”），区域字段自动带入其上级区域
+9. 必填项通过后保存成功，弹窗关闭，列表出现新设备
+10. 云端设备台账新增对应记录</x:v>
+      </x:c>
+      <x:c r="I10" s="8" t="str">
+        <x:v>核对设备名称、分类、类型、车间、区域、状态、入厂日期、二维码相关字段；回归所属分类智能下拉只影响该字段；所属车间按一二级层级显示且无同名一级重复项，二级车间写入“一级-二级”，下拉选项不展示场地编号。</x:v>
       </x:c>
       <x:c r="J10" s="8" t="inlineStr">
         <x:is>
@@ -1580,21 +1588,19 @@
       <x:c r="G12" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. 点击设备行编辑
-2. 修改型号、状态、车间、区域、备注
-3. 保存后重新打开详情</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 列表和详情展示更新后的字段
-2. 云端 data_update 成功
-3. 未修改字段保持不变</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">抽查百数云记录 data_id 未变化，字段值已更新。</x:t>
-        </x:is>
+2. 修改型号、状态、所属车间、区域、备注
+3. 分别验证所属车间可改为一级车间/区域或二级场地/部门
+4. 保存后重新打开详情</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" s="8" t="str">
+        <x:v>1. 列表和详情展示更新后的字段
+2. 所属车间按一级、二级层级展示且无同名一级重复项；选项不展示场地编号；选择一级时区域自动为同名一级区域，选择二级时车间显示/保存为“一级-二级”，区域自动为其上级区域
+3. 云端 data_update 成功
+4. 未修改字段保持不变</x:v>
+      </x:c>
+      <x:c r="I12" s="8" t="str">
+        <x:v>抽查百数云记录 data_id 未变化，字段值已更新；车间/区域字段与编辑弹窗最终选择一致，旧数据只存二级名称或场地编号时重新打开应能归一显示为“一级-二级”。</x:v>
       </x:c>
       <x:c r="J12" s="8" t="inlineStr">
         <x:is>
@@ -2178,16 +2184,13 @@
 2. 观察列表和新增弹窗下拉选项</x:t>
         </x:is>
       </x:c>
-      <x:c r="H22" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 列表展示编号、名称、状态、纳入点检、存放位置、最大存放量、包装形式、事故类型、责任人
-2. 下拉选项可搜索并能选择</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I22" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">核对关联选项来自对应底表或接口。</x:t>
-        </x:is>
+      <x:c r="H22" s="8" t="str">
+        <x:v>1. 列表展示编号、名称、状态、纳入点检、存放位置、最大存放量、包装形式、事故类型、责任人
+2. 下拉选项可搜索并能选择
+3. 存放位置下拉按场地一二级层级展示，一级可选，二级显示/保存为“一级-二级”，选项不展示场地编号</x:v>
+      </x:c>
+      <x:c r="I22" s="8" t="str">
+        <x:v>核对关联选项来自对应底表或接口；场地底表旧值只存二级名称或编号时仍可识别并归一显示。</x:v>
       </x:c>
       <x:c r="J22" s="8" t="inlineStr">
         <x:is>
@@ -2288,21 +2291,18 @@
           <x:t xml:space="preserve">存在危化品适用点检标准和责任人。</x:t>
         </x:is>
       </x:c>
-      <x:c r="G24" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 点击新增
+      <x:c r="G24" s="8" t="str">
+        <x:v>1. 点击新增
 2. 填写危化品名称、状态、是否纳入点检=是
-3. 选择点检标准、责任人、事故类型、存放位置、包装形式
+3. 选择点检标准、责任人、事故类型、存放位置、包装形式；存放位置分别验证一级和二级可选
 4. 填写最大存放量、使用量、危险有害性分析
-5. 保存</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 保存成功并出现在列表
+5. 保存</x:v>
+      </x:c>
+      <x:c r="H24" s="8" t="str">
+        <x:v>1. 保存成功并出现在列表
 2. 编号自动生成或唯一
-3. 纳入点检、标准、责任人等字段落库正确</x:t>
-        </x:is>
+3. 纳入点检、标准、责任人等字段落库正确
+4. 选择二级存放位置时写入“一级-二级”，不写入/展示场地编号；选择一级时使用地点自动带入同名一级区域</x:v>
       </x:c>
       <x:c r="I24" s="8" t="inlineStr">
         <x:is>
@@ -2413,12 +2413,10 @@
 3. 保存后重新打开</x:t>
         </x:is>
       </x:c>
-      <x:c r="H26" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 更新成功
-2. 历史值下拉显示为历史值并可保存
-3. 未修改字段保持不变</x:t>
-        </x:is>
+      <x:c r="H26" s="8" t="str">
+        <x:v>1. 更新成功
+2. 历史值下拉显示为历史值并可保存；若历史值能匹配场地底表二级名称或编号，重新打开应归一显示为“一级-二级”
+3. 未修改字段保持不变</x:v>
       </x:c>
       <x:c r="I26" s="8" t="inlineStr">
         <x:is>
@@ -2590,12 +2588,10 @@
 3. 未选择或无地点时重试</x:t>
         </x:is>
       </x:c>
-      <x:c r="H29" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 选中地点时打开打印页
-2. 打印页显示地点名称和二维码
-3. 无地点或未选择时给出明确提示</x:t>
-        </x:is>
+      <x:c r="H29" s="8" t="str">
+        <x:v>1. 选中地点时打开打印页
+2. 打印页显示地点名称、所属区域和二维码，不显示场地编码
+3. 无地点或未选择时给出明确提示</x:v>
       </x:c>
       <x:c r="I29" s="8" t="inlineStr">
         <x:is>
@@ -2708,12 +2704,11 @@
 3. 在报工页扫码危化品二维码</x:t>
         </x:is>
       </x:c>
-      <x:c r="H31" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 规则可生成危化品点检任务
+      <x:c r="H31" s="8" t="str">
+        <x:v>1. 规则可生成危化品点检任务
 2. 报工页识别对应危化品和任务
-3. 停用或不纳入点检的危化品不生成任务</x:t>
-        </x:is>
+3. 停用或不纳入点检的危化品不生成任务
+4. 危化品库匹配同时兼容二级名称、场地编号和“一级-二级”存放位置格式</x:v>
       </x:c>
       <x:c r="I31" s="8" t="inlineStr">
         <x:is>
@@ -2868,33 +2863,35 @@
       </x:c>
       <x:c r="E34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">新增点检标准主表并保存</x:t>
+          <x:t xml:space="preserve">新增点检标准主表并保存，主表不录入所属车间/区域</x:t>
         </x:is>
       </x:c>
       <x:c r="F34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">已在点检规则配置页面提前配置可选规则，例如日检、周检、月检；责任部门、负责人、车间区域可选。</x:t>
+          <x:t xml:space="preserve">已在点检规则配置页面提前配置可选规则，例如日检、周检、月检；责任部门、负责人可选。</x:t>
         </x:is>
       </x:c>
       <x:c r="G34" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. 点击新增
-2. 填写标准名称
-3. 选择执行规则、适用设备类型、状态、生效日期
-4. 选择责任部门/负责人，填写备注
-5. 保存</x:t>
+2. 确认标准主表弹窗不显示“所属车间”“所属区域”字段
+3. 填写标准名称
+4. 选择执行规则、适用设备类型、状态、生效日期
+5. 选择责任部门/负责人，填写备注
+6. 保存</x:t>
         </x:is>
       </x:c>
       <x:c r="H34" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. 标准编号自动生成或唯一
-2. 必填项通过后保存成功
-3. 新增标准出现在列表并可查看详情</x:t>
+2. 主表录入区无“所属车间”“所属区域”控件
+3. 必填项通过后保存成功
+4. 新增标准出现在列表并可查看详情</x:t>
         </x:is>
       </x:c>
       <x:c r="I34" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">标准主表字段：编号、名称、规则、适用类型、状态、版本、生效日期、责任部门、负责人。</x:t>
+          <x:t xml:space="preserve">标准主表字段：编号、名称、规则、适用类型、状态、版本、生效日期、责任部门、负责人；新增保存不依赖所属车间/所属区域，适用位置由后续关联对象体现。</x:t>
         </x:is>
       </x:c>
       <x:c r="J34" s="8" t="inlineStr">
@@ -2934,7 +2931,7 @@
       </x:c>
       <x:c r="F35" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">打开新增或编辑标准弹窗；执行规则下拉来自已配置的点检规则。</x:t>
+          <x:t xml:space="preserve">打开新增或编辑标准弹窗；执行规则下拉来自已配置的点检规则；主表弹窗不显示所属车间/所属区域。</x:t>
         </x:is>
       </x:c>
       <x:c r="G35" s="8" t="inlineStr">
@@ -2947,7 +2944,8 @@
       <x:c r="H35" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. 分别提示请填写标准名称、请选择执行规则、日期范围错误
-2. 不写入标准主表</x:t>
+2. 不写入标准主表
+3. 校验过程中不要求填写所属车间/所属区域</x:t>
         </x:is>
       </x:c>
       <x:c r="I35" s="8" t="inlineStr">
@@ -2995,20 +2993,26 @@
           <x:t xml:space="preserve">已打开标准编辑弹窗。</x:t>
         </x:is>
       </x:c>
-      <x:c r="G36" s="8" t="str">
-        <x:v>1. 点击明细新增
+      <x:c r="G36" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 点击明细新增
 2. 填写序号、点检部位、点检项目名称、执行方式=普通、点检类型、标准内容
 3. 确认页面没有“是否报工”选项
-4. 保存明细并保存标准</x:v>
-      </x:c>
-      <x:c r="H36" s="8" t="str">
-        <x:v>1. 明细行新增成功
+4. 保存明细并保存标准</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H36" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 明细行新增成功
 2. 序号排序正确
 3. 明细默认参与报工，底表是否报工/启用字段写入“启用”
-4. 保存标准后明细落入点检标准明细表</x:v>
-      </x:c>
-      <x:c r="I36" s="8" t="str">
-        <x:v>核对明细表 standardId、standardName、seq、pointItem、checkMethod、enabledStatus；报工端可识别该明细。</x:v>
+4. 保存标准后明细落入点检标准明细表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I36" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对明细表 standardId、standardName、seq、pointItem、checkMethod、enabledStatus；报工端可识别该明细。</x:t>
+        </x:is>
       </x:c>
       <x:c r="J36" s="8" t="inlineStr">
         <x:is>
@@ -3099,26 +3103,36 @@
           <x:t xml:space="preserve">P0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E38" s="8" t="str">
-        <x:v>执行方式为抄表时要求参数单位，并支持闭区间/单边条件判断标准</x:v>
-      </x:c>
-      <x:c r="F38" s="8" t="str">
-        <x:v>已打开明细新增弹窗。</x:v>
-      </x:c>
-      <x:c r="G38" s="8" t="str">
-        <x:v>1. 选择执行方式=抄表
+      <x:c r="E38" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">执行方式为抄表时要求参数单位，并支持闭区间/单边条件判断标准</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已打开明细新增弹窗。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G38" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 选择执行方式=抄表
 2. 不填参数单位保存
 3. 填写单位但判断标准为空或格式无效后保存
-4. 填写 48-80、&gt;10、&gt;=10、&lt;5、&lt;=5 等判断标准后保存</x:v>
-      </x:c>
-      <x:c r="H38" s="8" t="str">
-        <x:v>1. 缺单位提示请填写参数单位
+4. 填写 48-80、&gt;10、&gt;=10、&lt;5、&lt;=5 等判断标准后保存</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H38" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 缺单位提示请填写参数单位
 2. 缺判断标准提示填写数值范围或单边条件
 3. 合法闭区间和单边条件均可保存
-4. 保存到底表的判断标准保留完整表达式，报工页可据此自动判定正常/异常</x:v>
-      </x:c>
-      <x:c r="I38" s="8" t="str">
-        <x:v>单边条件用于表达“高于/低于某值即正常”，例如 &gt;10 表示大于 10 正常。</x:v>
+4. 保存到底表的判断标准保留完整表达式，报工页可据此自动判定正常/异常</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I38" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">单边条件用于表达“高于/低于某值即正常”，例如 &gt;10 表示大于 10 正常。</x:t>
+        </x:is>
       </x:c>
       <x:c r="J38" s="8" t="inlineStr">
         <x:is>
@@ -3395,23 +3409,18 @@
           <x:t xml:space="preserve">存在启用并纳入点检的危化品。</x:t>
         </x:is>
       </x:c>
-      <x:c r="G43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 选择适用设备类型=危化品
+      <x:c r="G43" s="8" t="str">
+        <x:v>1. 选择适用设备类型=危化品
 2. 点击关联对象
-3. 选择危化品确认</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 危化品可关联并展示事故类型/风险信息
-2. 停用或不符合条件对象不可关联或不参与后续任务</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I43" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">关联表 objectType=危化品，后续规则任务能识别该对象。</x:t>
-        </x:is>
+3. 在对象选择表搜索并选择危化品库确认</x:v>
+      </x:c>
+      <x:c r="H43" s="8" t="str">
+        <x:v>1. 危化品库可关联并展示事故类型/风险信息
+2. 选择表不显示场地编码列，场地名称按“一级-二级”展示
+3. 停用或不符合条件对象不可关联或不参与后续任务</x:v>
+      </x:c>
+      <x:c r="I43" s="8" t="str">
+        <x:v>关联表 objectType=危化品，后续规则任务能识别该对象；危化品库匹配兼容二级名称、场地编号和“一级-二级”格式。</x:v>
       </x:c>
       <x:c r="J43" s="8" t="inlineStr">
         <x:is>
@@ -4631,7 +4640,7 @@
       </x:c>
       <x:c r="E64" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">所有点检项填写正常后提交汇总</x:t>
+          <x:t xml:space="preserve">所有点检项填写正常后提交汇总并展示完成页</x:t>
         </x:is>
       </x:c>
       <x:c r="F64" s="8" t="inlineStr">
@@ -4648,15 +4657,15 @@
       </x:c>
       <x:c r="H64" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1. 提交成功
-2. 生成报工主表和明细
-3. 任务状态更新为已完成，报工状态为已报工
-4. 完成页显示结果正常、异常数 0</x:t>
+          <x:t xml:space="preserve">1. 所有明细判定正常后提交成功
+2. 报工主表结果为正常，明细全部 abnormal=否
+3. 提交成功页展示点检完成、整体统计和返回/下一任务按钮
+4. 提交成功页不展示异常明细卡片，不显示“报工已提交：提交ID”状态条</x:t>
         </x:is>
       </x:c>
       <x:c r="I64" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">核对报工主表、报工明细表、任务底表 reportedCount/reportStatus。</x:t>
+          <x:t xml:space="preserve">核对报工主表 reportStatus/result、任务状态与完成页展示；成功页风格与安全检查移动端提交后整体信息页保持一致。</x:t>
         </x:is>
       </x:c>
       <x:c r="J64" s="8" t="inlineStr">
@@ -4691,32 +4700,33 @@
       </x:c>
       <x:c r="E65" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">点检异常项提交后生成隐患整改流程</x:t>
+          <x:t xml:space="preserve">点检异常项处理情况控制隐患工单闭环状态</x:t>
         </x:is>
       </x:c>
       <x:c r="F65" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">点检明细设置异常描述或照片必填，任务未执行。</x:t>
+          <x:t xml:space="preserve">点检明细设置异常描述或照片必填，任务未执行；异常项支持处理情况“待处理/已处理”。</x:t>
         </x:is>
       </x:c>
       <x:c r="G65" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1. 将一个项目标记异常
+          <x:t xml:space="preserve">1. 将一个项目标记异常并保持处理情况为待处理
 2. 不填必填异常描述/照片提交
-3. 补齐异常描述、照片、处理措施后提交</x:t>
+3. 补齐异常描述、照片、处理措施后提交
+4. 另选任务将异常项处理情况改为已处理后提交</x:t>
         </x:is>
       </x:c>
       <x:c r="H65" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. 缺必填项时前端拦截
-2. 补齐后提交成功且结果为异常
-3. 报工明细 abnormal=是
-4. 隐患整改工单创建并发起流程</x:t>
+2. 待处理异常提交成功且结果为异常，隐患工单通过 flow_start 创建，状态为待整改
+3. 已处理异常提交成功且结果仍为异常，隐患留痕状态为已关闭并写关闭时间，不产生待整改任务
+4. 全部异常均已处理时点检任务状态为已完成，存在待处理异常时任务状态为异常</x:t>
         </x:is>
       </x:c>
       <x:c r="I65" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">核对隐患表 source=点巡检、beforePhotos、deadline、requirement，flow_start 成功。</x:t>
+          <x:t xml:space="preserve">核对隐患表 source=点巡检、status、closedAt、beforePhotos、deadline、requirement；确认 safety-check 来源仍写安全检查且不受影响。</x:t>
         </x:is>
       </x:c>
       <x:c r="J65" s="8" t="inlineStr">
@@ -4749,24 +4759,34 @@
           <x:t xml:space="preserve">P0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E66" s="8" t="str">
-        <x:v>抄表数值根据闭区间或单边条件判断标准自动判定正常/异常</x:v>
-      </x:c>
-      <x:c r="F66" s="8" t="str">
-        <x:v>标准明细执行方式=抄表，判断标准可为 48-80 或 &gt;10。</x:v>
-      </x:c>
-      <x:c r="G66" s="8" t="str">
-        <x:v>1. 使用闭区间标准输入范围内/范围外数值
+      <x:c r="E66" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">抄表数值根据闭区间或单边条件判断标准自动判定正常/异常</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F66" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">标准明细执行方式=抄表，判断标准可为 48-80 或 &gt;10。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G66" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 使用闭区间标准输入范围内/范围外数值
 2. 使用 &gt;10 标准输入 11、10、9 等数值
-3. 提交前观察自动判定</x:v>
-      </x:c>
-      <x:c r="H66" s="8" t="str">
-        <x:v>1. 48-80 范围内判定正常，超出判定异常
+3. 提交前观察自动判定</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H66" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 48-80 范围内判定正常，超出判定异常
 2. &gt;10 时 11 判定正常，10 和 9 判定异常
-3. 异常时要求异常信息，实际数值写入报工明细 actualNumericValue</x:v>
-      </x:c>
-      <x:c r="I66" s="8" t="str">
-        <x:v>核对自动判定详情展示标准条件；兼容 &gt;=、&lt;、&lt;= 及常见中文写法。</x:v>
+3. 异常时要求异常信息，实际数值写入报工明细 actualNumericValue</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I66" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对自动判定详情展示标准条件；兼容 &gt;=、&lt;、&lt;= 及常见中文写法。</x:t>
+        </x:is>
       </x:c>
       <x:c r="J66" s="8" t="inlineStr">
         <x:is>
@@ -5966,20 +5986,26 @@
           <x:t xml:space="preserve">模板某项配置异常说明或照片必填。</x:t>
         </x:is>
       </x:c>
-      <x:c r="G86" s="8" t="str">
-        <x:v>1. 将该项选择异常
+      <x:c r="G86" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 将该项选择异常
 2. 查看整改要求下方的处理情况，保持默认待处理
 3. 不填模板要求的异常说明或照片提交
-4. 补充异常说明和照片后提交</x:v>
-      </x:c>
-      <x:c r="H86" s="8" t="str">
-        <x:v>1. 缺失必填项时拦截
+4. 补充异常说明和照片后提交</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H86" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 缺失必填项时拦截
 2. 处理情况默认待处理
 3. 提交后结果为异常，异常数正确
-4. 生成待整改隐患工单并关联提交明细</x:v>
-      </x:c>
-      <x:c r="I86" s="8" t="str">
-        <x:v>核对提交明细处理情况字段 _widget_1780483037794=待处理；hazard 表 source=安全检查、submissionId/submissionDetailId、状态=待整改。</x:v>
+4. 生成待整改隐患工单并关联提交明细</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I86" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对提交明细处理情况字段 _widget_1780483037794=待处理；hazard 表 source=安全检查、submissionId/submissionDetailId、状态=待整改。</x:t>
+        </x:is>
       </x:c>
       <x:c r="J86" s="8" t="inlineStr">
         <x:is>
@@ -6193,37 +6219,51 @@
           <x:t xml:space="preserve">P0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E90" s="8" t="str">
-        <x:v>安全检查记录查询、详情、打印和导出</x:v>
-      </x:c>
-      <x:c r="F90" s="8" t="str">
-        <x:v>存在正常和异常检查提交记录；至少一条记录包含现场签名，以及异常项说明、整改要求/措施、处理情况和异常照片。</x:v>
-      </x:c>
-      <x:c r="G90" s="8" t="str">
-        <x:v>1. 从百数云菜单进入检查记录页面
+      <x:c r="E90" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">安全检查记录分页查询、检查时间编辑、详情、批量打印和导出</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F90" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">存在正常和异常检查提交记录；至少一条记录包含现场签名，以及异常项说明、整改要求/措施、处理情况和异常照片。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G90" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 从百数云菜单进入检查记录页面
 2. 按提交编号、检查类型、检查人、区域对象搜索
 3. 按结果筛选，观察分页是否回到第 1 页
 4. 切换每页 10/20/50 条并翻页
 5. 点击详情查看明细
-6. 勾选一条或多条记录，在顶部菜单点击打印和导出
-7. 切换打印模板后再次批量打印/导出</x:v>
-      </x:c>
-      <x:c r="H90" s="8" t="str">
-        <x:v>1. 页面右上角不显示刷新按钮，底部不显示“准备就绪”状态栏
+6. 在详情弹窗右下角点击编辑，确认检查时间在当前详情弹窗内变成可编辑输入框
+7. 修改检查时间并在当前详情弹窗内保存
+8. 勾选一条或多条记录，在顶部菜单点击打印和导出
+9. 切换打印模板后再次批量打印/导出</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H90" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 页面右上角不显示刷新按钮，底部不显示“准备就绪”状态栏
 2. 列表默认每页 10 条，分页条展示总数、当前显示范围、页码和上一页/下一页；可切换 10/20/50 条每页
 3. 筛选条件变化后回到第 1 页；表头全选只选择当前页，跨页已勾选记录在当前筛选结果内保留
-4. 列表展示提交编号、检查类型、区域、检查人、结束时间、结果、异常数、状态；表格内容垂直居中，结果、异常数、状态、操作等短字段居中显示
-5. 行内只保留详情操作，打印和导出位于顶部菜单栏；勾选多条记录后可批量打印/导出，未勾选时可处理当前选中行
-6. 详情展示每项结果、异常说明、整改要求/措施、处理情况、异常照片和整改流程；异常照片以缩略图显示，不只显示文件链接，并展示现场签名图片
-7. 打印支持结果检查表和记录检查表两套模板，标题不重复“检查”，A4 页面表格宽度、元信息、签名和日期布局贴近检查表模板
-8. 明细打印模板顶部显示检查日期和检查人员签字，不显示单位名称；底部不再重复检查人员和检查日期
-9. 底部检查人员和检查日期两侧填写栏等高、横线对齐，签名图片尺寸受控，不撑高左侧栏
-10. 右侧“如不符合”列仅异常项填写存在问题和整改措施，正常项为空，不带现场照片、签字时间、异常照片或整改流程编号
-11. 检查人员取签名子表手写签名字段并显示签名图片，多个签名以“、”分隔，不取主表检查人/提交人；检查日期带出结束时间日期
-12. 导出文件可用 Excel 打开且不影响其他安全检查页面</x:v>
-      </x:c>
-      <x:c r="I90" s="8" t="str">
-        <x:v>分页仅影响列表展示；批量打印/导出按已勾选记录处理，表头全选仅选择当前页。</x:v>
+4. 列表展示提交编号、检查类型、区域、检查人、检查时间、结果、异常数、状态；表格内容垂直居中，结果、异常数、状态、操作等短字段居中显示；行内操作只显示详情
+5. 详情弹窗右下角显示编辑按钮；点击后不打开新的页面或二级弹窗，而是在当前详情弹窗内把检查时间切换为可编辑输入框，并显示取消/保存按钮
+6. 保存后回写安全检查提交主表结束时间字段，当前详情弹窗恢复展示态，列表/详情中的检查时间刷新
+7. 打印和导出位于顶部菜单栏；勾选多条记录后可批量打印/导出，未勾选时可处理当前选中行
+8. 详情展示每项结果、异常说明、整改要求/措施、处理情况、异常照片和整改流程；异常照片以缩略图显示，不只显示文件链接，并展示现场签名图片
+9. 打印支持结果检查表和记录检查表两套模板，标题不重复“检查”，A4 页面表格宽度、元信息、签名和日期布局贴近检查表模板
+10. 明细打印模板顶部显示检查日期和检查人员签字，不显示单位名称；底部不再重复检查人员和检查日期
+11. 底部检查人员和检查日期两侧填写栏等高、横线对齐，签名图片尺寸受控，不撑高左侧栏
+12. 右侧“如不符合”列仅异常项填写存在问题和整改措施，正常项为空，不带现场照片、签字时间、异常照片或整改流程编号
+13. 检查人员取签名子表手写签名字段并显示签名图片，多个签名以“、”分隔，不取主表检查人/提交人；检查日期带出检查时间日期
+14. 导出文件可用 Excel 打开且不影响其他安全检查页面</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I90" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">分页仅影响列表展示；批量打印/导出按已勾选记录处理，表头全选仅选择当前页。编辑检查时间入口位于详情弹窗右下角，点击后在当前详情弹窗内联编辑，只更新提交主表 endTime，不修改检查明细、签名或隐患数据。</x:t>
+        </x:is>
       </x:c>
       <x:c r="J90" s="8" t="inlineStr">
         <x:is>
@@ -6373,32 +6413,44 @@
           <x:t xml:space="preserve">P0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E93" s="8" t="str">
-        <x:v>相关方培训记录分页查询、弹窗详情和打印</x:v>
+      <x:c r="E93" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">相关方培训记录分页查询、弹窗详情和批量打印删除</x:t>
+        </x:is>
       </x:c>
       <x:c r="F93" s="8" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">培训记录表和相关方单位台账有数据。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G93" s="8" t="str">
-        <x:v>1. 从百数云菜单进入相关方培训管理页面
-2. 查看培训记录表格，不展示左侧重复记录列表
-3. 搜索标题/单位/项目
-4. 切换每页 10/20/50 条并翻页
-5. 点击表格行内详情查看弹窗
-6. 点击行内打印或选中记录后点击顶部打印</x:v>
-      </x:c>
-      <x:c r="H93" s="8" t="str">
-        <x:v>1. 页面以培训记录为主视图，展示编号、标题、培训日期、施工单位、人数、项目、授课人、是否抽取和操作
-2. 页面不内嵌二维码生成区，顶部提供二维码下载入口
+          <x:t xml:space="preserve">培训记录表和相关方单位台账有数据，存在多条可勾选记录。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G93" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 从百数云菜单进入相关方培训管理页面
+2. 查看页头按钮和标题区，不展示刷新、新建、编辑按钮及标题下说明文案
+3. 查看标题下方工具栏，二维码下载/打印/删除在左侧，搜索框/搜索/重置在右侧，不显示蓝色扫码提示条
+4. 查看培训记录表格，不展示左侧重复记录列表，不展示编号、标题、施工项目列
+5. 使用培训日期/施工单位/授课人关键字搜索
+6. 切换每页 10/20/50 条并翻页，默认每页 10 条
+7. 点击表格行内详情，确认详情以弹窗展示且详情中不展示施工项目
+8. 勾选单条或多条记录后点击页头工具栏打印、删除按钮</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H93" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 页面以培训记录为主视图，页头仅显示标题；标题下方工具栏左侧保留二维码下载、打印、删除，右侧展示搜索框、搜索、重置；打印/删除未勾选记录时仍正常显示，点击后提示未选择数据，勾选后按钮文案仍为“打印”“删除”，不显示括号数量
+2. 页面不内嵌二维码生成区，二维码下载跳转独立页面，且管理页不显示蓝色扫码提示条
 3. 列表默认每页 10 条，分页条展示总数、当前范围、页码和上一页/下一页，可切换 10/20/50 条每页
-4. 点击详情后以弹窗展示主表和参训人员签字明细，数据列表下方不再显示详情卡片
-5. 打印打开《相关方入厂安全告知书》模板，固定条款与模板一致
-6. 打印模板从记录带出相关方人员签名、施工单位名称和培训日期；相关方人员签名只展示手写签名图片，不展示姓名，未手写签名人员不展示</x:v>
-      </x:c>
-      <x:c r="I93" s="8" t="str">
-        <x:v>核对培训记录主表和参训人员子表签字字段；打印只带出模板要求的动态字段。</x:v>
+4. 列表列包含勾选框、培训日期、施工单位、培训人数、授课人、是否抽取、操作，不显示编号、标题、施工项目
+5. 点击详情后以弹窗展示主表和参训人员签字明细，数据列表下方不显示详情卡片，详情中不显示施工项目
+6. 勾选多条后点击打印可批量打开《相关方入厂安全告知书》打印页，按记录分页输出
+7. 勾选多条后点击删除只删除已勾选记录，并有二次确认
+8. 打印模板从记录带出相关方人员签名、施工单位名称和培训日期；相关方人员签名只展示手写签名图片，不展示姓名，未手写签名人员不展示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I93" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对培训记录主表和参训人员子表签字字段；批量操作只作用于表格勾选记录。</x:t>
+        </x:is>
       </x:c>
       <x:c r="J93" s="8" t="inlineStr">
         <x:is>
@@ -6430,30 +6482,38 @@
           <x:t xml:space="preserve">P0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E94" s="8" t="str">
-        <x:v>独立二维码下载页生成静态入口码和单位预填码</x:v>
+      <x:c r="E94" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">独立二维码下载页生成静态入口码和单位预填码</x:t>
+        </x:is>
       </x:c>
       <x:c r="F94" s="8" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">PUBLIC_BASE_URL 或可访问内网地址配置正确，单位台账有数据。</x:t>
         </x:is>
       </x:c>
-      <x:c r="G94" s="8" t="str">
-        <x:v>1. 从管理页点击二维码下载入口或从百数云菜单进入二维码下载页
+      <x:c r="G94" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 从管理页点击二维码下载入口或从百数云菜单进入二维码下载页
 2. 选择二维码类型=静态入口码
 3. 复制链接、下载二维码、打开二维码和入口页
 4. 切换为单位预填码，搜索并选择施工单位
-5. 下载该单位预填码并扫码打开</x:v>
-      </x:c>
-      <x:c r="H94" s="8" t="str">
-        <x:v>1. 二维码下载页与培训记录页分离，培训记录页不重复展示二维码配置
+5. 下载该单位预填码并扫码打开</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H94" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 二维码下载页与培训记录页分离，培训记录页不重复展示二维码配置
 2. 静态入口码进入填报页但不预填单位
 3. 单位预填码进入填报页并选中对应施工单位
 4. 二维码图片可下载、打开和扫码访问
-5. 切换二维码类型或施工单位后二维码、链接和文件名同步更新</x:v>
-      </x:c>
-      <x:c r="I94" s="8" t="str">
-        <x:v>二维码独立页使用 /h5/partner-training-qr；直接 .html 公网路径当前会被 Nginx 旧静态文件截走，不作为菜单入口。</x:v>
+5. 切换二维码类型或施工单位后二维码、链接和文件名同步更新</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I94" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">二维码独立页使用 /h5/partner-training-qr；直接 .html 公网路径当前会被 Nginx 旧静态文件截走，不作为菜单入口。</x:t>
+        </x:is>
       </x:c>
       <x:c r="J94" s="8" t="inlineStr">
         <x:is>
@@ -7033,32 +7093,24 @@
           <x:t xml:space="preserve">公开填报页车间来源于场地底表并提交车间负责人</x:t>
         </x:is>
       </x:c>
-      <x:c r="F104" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">场地底表存在场地名称、场地编码、所属区域；通讯录成员可加载。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G104" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 进入相关方入场培训填报页
+      <x:c r="F104" s="8" t="str">
+        <x:v>场地底表存在场地名称、所属区域及上下级关系；通讯录成员可加载。</x:v>
+      </x:c>
+      <x:c r="G104" s="8" t="str">
+        <x:v>1. 进入相关方入场培训填报页
 2. 展开车间下拉
-3. 按区域选择一个车间
+3. 在层级中先选择一级车间/区域，再选择同一一级下的二级场地/部门
 4. 查看车间负责人是否自动带出；无默认负责人时手动选择负责人
-5. 完成其他必填项后提交</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H104" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 车间下拉与设备台账“所属车间”一致，按所属区域分组，展示名称和编码
+5. 完成其他必填项后提交</x:v>
+      </x:c>
+      <x:c r="H104" s="8" t="str">
+        <x:v>1. 车间下拉与设备台账“所属车间”一致，按场地原一二级层级展示，一级可直接选择，二级显示/保存为“一级-二级”，选项不展示场地编号
 2. 车间值写入主表字段 _widget_1779173632236
 3. 车间负责人写入主表字段 _widget_1779173632260
-4. 不影响施工单位、授课人、签字和图片上传</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I104" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">核对场地底表 entryId=099e47809199d1d8214a984f；核对培训记录主表车间、车间负责人字段。</x:t>
-        </x:is>
+4. 不影响施工单位、授课人、签字和图片上传</x:v>
+      </x:c>
+      <x:c r="I104" s="8" t="str">
+        <x:v>核对场地底表 entryId=099e47809199d1d8214a984f；核对培训记录主表车间、车间负责人字段；旧数据只存二级名称或编号时应兼容识别。</x:v>
       </x:c>
       <x:c r="J104" s="8" t="inlineStr">
         <x:is>
@@ -7665,214 +7717,366 @@
       </x:c>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" t="str">
-        <x:v>PART-013</x:v>
-      </x:c>
-      <x:c r="B115" t="str">
-        <x:v>相关方培训填报</x:v>
-      </x:c>
-      <x:c r="C115" t="str">
-        <x:v>危险作业附件</x:v>
-      </x:c>
-      <x:c r="D115" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="E115" t="str">
-        <x:v>选择危险作业时必须上传危险作业附件</x:v>
-      </x:c>
-      <x:c r="F115" t="str">
-        <x:v>使用相关方入场培训填报入口；施工单位、授课人、车间等选项加载成功；准备 1 个危险作业附件文件。</x:v>
-      </x:c>
-      <x:c r="G115" t="str">
-        <x:v>1. 阅读安全告知后进入填报页
+      <x:c r="A115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PART-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">相关方培训填报</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">危险作业附件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">P1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">选择危险作业时必须上传特种作业附件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">使用相关方入场培训填报入口；施工单位、授课人、车间等选项加载成功；准备 1 个特种作业附件文件。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 阅读安全告知后进入填报页
 2. 是否危险作业保持未选，尝试提交
 3. 选择是否危险作业=是，未上传附件时提交
-4. 上传危险作业附件后完成参训人员签字并提交
-5. 重新进入并选择是否危险作业=否，不上传附件后提交</x:v>
-      </x:c>
-      <x:c r="H115" t="str">
-        <x:v>1. 未选择是否危险作业时提示必须选择
-2. 选择“是”后危险作业附件上传标题显示红色必填标记，未上传附件时不允许提交
+4. 上传特种作业附件后完成参训人员签字并提交
+5. 重新进入并选择是否危险作业=否，不上传附件后提交</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 未选择是否危险作业时提示必须选择
+2. 选择“是”后“特种作业附件上传”标题显示红色必填标记，未上传附件时不允许提交
 3. 上传附件后可提交成功，附件卡片可预览/删除
-4. 选择“否”时附件必填标记隐藏，附件不强制上传，仍可提交</x:v>
-      </x:c>
-      <x:c r="I115" t="str">
-        <x:v>核对培训记录主表字段：是否危险作业 _widget_1780365156595，危险作业附件上传 _widget_1780365156616；附件通过 upload_file 返回文件对象后回填主表字段。</x:v>
-      </x:c>
-      <x:c r="J115" t="str">
-        <x:v>移动端手工</x:v>
-      </x:c>
-      <x:c r="K115"/>
-      <x:c r="L115"/>
+4. 选择“否”时附件必填标记隐藏，附件不强制上传，仍可提交</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对培训记录主表字段：是否危险作业 _widget_1780365156595，危险作业附件上传 _widget_1780365156616；页面展示标题为“特种作业附件上传”，附件通过 upload_file 返回文件对象后回填主表字段。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J115" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">移动端手工</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="116">
-      <x:c r="A116" t="str">
-        <x:v>DEV-016</x:v>
-      </x:c>
-      <x:c r="B116" t="str">
-        <x:v>设备台账</x:v>
-      </x:c>
-      <x:c r="C116" t="str">
-        <x:v>列表分页</x:v>
-      </x:c>
-      <x:c r="D116" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="E116" t="str">
-        <x:v>设备数量较多时列表分页且使用标准区域保持可见</x:v>
-      </x:c>
-      <x:c r="F116" t="str">
-        <x:v>设备台账中准备超过 30 台设备，且至少一个分类下存在多台设备。</x:v>
-      </x:c>
-      <x:c r="G116" t="str">
-        <x:v>1. 从百数云菜单进入设备台账
+      <x:c r="A116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DEV-016</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">设备台账</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">列表分页</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">P1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">设备数量较多时列表分页且使用标准区域保持可见</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">设备台账中准备超过 30 台设备，且至少一个分类下存在多台设备。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 从百数云菜单进入设备台账
 2. 选择全部设备或数量较多的设备分类
 3. 查看表格底部分页条和使用标准区域
 4. 切换上一页/下一页/页码和每页条数
-5. 勾选表头复选框</x:v>
-      </x:c>
-      <x:c r="H116" t="str">
-        <x:v>1. 默认每页显示 20 台设备，不因设备过多把使用标准区域挤出页面
+5. 勾选表头复选框</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 默认每页显示 20 台设备，不因设备过多把使用标准区域挤出页面
 2. 分页条显示当前页、总页数和当前页范围
 3. 切换页码或每页条数后表格内容更新且布局保持清晰
 4. 表头复选框只选择/取消当前页设备
-5. 点击设备后下方使用标准区域仍可查看</x:v>
-      </x:c>
-      <x:c r="I116" t="str">
-        <x:v>核对筛选总数、当前页范围、已选择数量与页面展示一致；不影响导出和批量打印使用当前筛选结果。</x:v>
-      </x:c>
-      <x:c r="J116" t="str">
-        <x:v>手工</x:v>
-      </x:c>
-      <x:c r="K116"/>
-      <x:c r="L116"/>
+5. 点击设备后下方使用标准区域仍可查看</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对筛选总数、当前页范围、已选择数量与页面展示一致；不影响导出和批量打印使用当前筛选结果。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J116" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">手工</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="117">
-      <x:c r="A117" t="str">
-        <x:v>CHEM-011</x:v>
-      </x:c>
-      <x:c r="B117" t="str">
-        <x:v>危化品台账</x:v>
-      </x:c>
-      <x:c r="C117" t="str">
-        <x:v>列表分页</x:v>
-      </x:c>
-      <x:c r="D117" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="E117" t="str">
-        <x:v>危化品数量较多时列表默认 20 条分页展示</x:v>
-      </x:c>
-      <x:c r="F117" t="str">
-        <x:v>危化品台账中准备超过 20 条危化品记录，且至少一个地点或全部地点筛选结果超过 20 条。</x:v>
-      </x:c>
-      <x:c r="G117" t="str">
-        <x:v>1. 从百数云菜单进入危化品台账
+      <x:c r="A117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CHEM-011</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">危化品台账</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">列表分页</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">P1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">危化品数量较多时列表默认 20 条分页展示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">危化品台账中准备超过 20 条危化品记录，且至少一个地点或全部地点筛选结果超过 20 条。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 从百数云菜单进入危化品台账
 2. 选择全部地点或数量较多的危化品地点
 3. 查看表格底部分页条
 4. 切换上一页/下一页/页码和每页条数
-5. 执行关键字、状态或地点树筛选后再次查看分页</x:v>
-      </x:c>
-      <x:c r="H117" t="str">
-        <x:v>1. 默认每页显示 20 条危化品记录，避免大量行挤满页面
+5. 执行关键字、状态或地点树筛选后再次查看分页</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 默认每页显示 20 条危化品记录，避免大量行挤满页面
 2. 分页条显示当前页、总页数和当前页范围
 3. 切换页码或每页条数后表格内容更新且布局保持清晰
 4. 搜索、状态筛选、地点树切换后自动回到第一页
-5. 导出仍按当前筛选结果全量导出，不只导出当前页</x:v>
-      </x:c>
-      <x:c r="I117" t="str">
-        <x:v>核对底部统计中的总数、当前筛选数、当前页范围与页面展示一致；分页不影响详情、编辑、删除和导出。</x:v>
-      </x:c>
-      <x:c r="J117" t="str">
-        <x:v>手工</x:v>
-      </x:c>
-      <x:c r="K117"/>
-      <x:c r="L117"/>
+5. 导出仍按当前筛选结果全量导出，不只导出当前页</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对底部统计中的总数、当前筛选数、当前页范围与页面展示一致；分页不影响详情、编辑、删除和导出。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J117" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">手工</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="118">
-      <x:c r="A118" t="str">
-        <x:v>STD-016</x:v>
-      </x:c>
-      <x:c r="B118" t="str">
-        <x:v>点检标准</x:v>
-      </x:c>
-      <x:c r="C118" t="str">
-        <x:v>明细必填和提示</x:v>
-      </x:c>
-      <x:c r="D118" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="E118" t="str">
-        <x:v>明细默认报工、必填标识和顶部校验提示</x:v>
-      </x:c>
-      <x:c r="F118" t="str">
-        <x:v>打开新增或编辑点检标准弹窗；准备普通、状态、抄表三类明细。</x:v>
-      </x:c>
-      <x:c r="G118" t="str">
-        <x:v>1. 查看点检明细表头和明细弹窗标签
+      <x:c r="A118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">STD-016</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">点检标准</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">明细必填和提示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">P1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">明细默认报工、必填标识和顶部校验提示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">打开新增或编辑点检标准弹窗；准备普通、状态、抄表三类明细。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 查看点检明细表头和明细弹窗标签
 2. 不填写点检部位、点检项目名称、执行方式或标准内容后保存
 3. 选择执行方式=抄表，不填参数单位或判断标准范围后保存
 4. 查看错误提示位置
-5. 填写完整后保存标准</x:v>
-      </x:c>
-      <x:c r="H118" t="str">
-        <x:v>1. 页面不展示“是否报工”列或下拉，明细默认全部参与报工
+5. 填写完整后保存标准</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 页面不展示“是否报工”列或下拉，明细默认全部参与报工
 2. 点检部位、点检项目名称、执行方式、标准内容显示必填标识
 3. 抄表方式下参数单位和判断标准范围显示必填并被校验
 4. 校验失败提示在页面顶部醒目显示，不出现在右下角
-5. 填写完整后可保存，明细底表 enabledStatus 写入“启用”</x:v>
-      </x:c>
-      <x:c r="I118" t="str">
-        <x:v>核对新增/编辑标准整表保存、单条明细保存、行内保存三种入口；不合规时不调用或不完成保存。</x:v>
-      </x:c>
-      <x:c r="J118" t="str">
-        <x:v>手工</x:v>
-      </x:c>
-      <x:c r="K118"/>
-      <x:c r="L118"/>
+5. 填写完整后可保存，明细底表 enabledStatus 写入“启用”</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对新增/编辑标准整表保存、单条明细保存、行内保存三种入口；不合规时不调用或不完成保存。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J118" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">手工</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="119">
-      <x:c r="A119" t="str">
-        <x:v>SCMOB-008</x:v>
-      </x:c>
-      <x:c r="B119" t="str">
-        <x:v>安全检查 H5</x:v>
-      </x:c>
-      <x:c r="C119" t="str">
-        <x:v>处理情况闭环</x:v>
-      </x:c>
-      <x:c r="D119" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="E119" t="str">
-        <x:v>异常项处理情况控制隐患工单闭环状态</x:v>
-      </x:c>
-      <x:c r="F119" t="str">
-        <x:v>准备包含至少两项检查项的安全检查任务；其中两项可选择异常，一项现场已处理，一项待后续处理。</x:v>
-      </x:c>
-      <x:c r="G119" t="str">
-        <x:v>1. 进入安全检查 H5 执行任务
+      <x:c r="A119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SCMOB-008</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">安全检查 H5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">处理情况闭环</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">P1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">异常项处理情况控制隐患工单闭环状态</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">准备包含至少两项检查项的安全检查任务；其中两项可选择异常，一项现场已处理，一项待后续处理。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 进入安全检查 H5 执行任务
 2. 将第一项选择异常，填写异常说明、整改要求，处理情况选择已处理
 3. 将第二项选择异常，填写异常说明、整改要求，处理情况保持待处理
 4. 提交检查并查看完成页
-5. 在安全检查记录和隐患工单中核对两条异常</x:v>
-      </x:c>
-      <x:c r="H119" t="str">
-        <x:v>1. 处理情况控件位于整改要求下方，选项为已处理、待处理，默认待处理
+5. 在安全检查记录和隐患工单中核对两条异常</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 处理情况控件位于整改要求下方，选项为已处理、待处理，默认待处理
 2. 提交明细底表 _widget_1780483037794 分别写入已处理/待处理
 3. 已处理异常仍生成隐患工单留痕，工单状态直接为已关闭并有关闭时间
 4. 待处理异常沿用原逻辑，生成待整改流程工单
 5. 同次检查只要存在待处理异常，任务状态为异常待整改；若异常全部已处理，任务状态为已完成
-6. 安全检查记录详情展示处理情况</x:v>
-      </x:c>
-      <x:c r="I119" t="str">
-        <x:v>核对 /api/safety-check/submit 返回 hazardIds、flowIds、closedHazardIds、pendingAbnormalCount、closedHazardCount；核对隐患底表状态和提交明细字段。</x:v>
-      </x:c>
-      <x:c r="J119" t="str">
-        <x:v>集成手工</x:v>
-      </x:c>
-      <x:c r="K119"/>
-      <x:c r="L119"/>
+6. 安全检查记录详情展示处理情况</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对 /api/safety-check/submit 返回 hazardIds、flowIds、closedHazardIds、pendingAbnormalCount、closedHazardCount；核对隐患底表状态和提交明细字段。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J119" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">集成手工</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SCMOB-009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">安全检查 H5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主要负责人签字与暂存</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">P1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主要负责人签字选填并支持检查草稿暂存恢复</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">准备一条待检查任务，检查模板含正常/异常检查项；移动端浏览器允许 localStorage。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 进入安全检查 H5，选择检查人并打开待检查任务
+2. 填写部分检查项结果、异常说明/整改要求/处理情况，上传异常照片或现场照片
+3. 在现场人员签名下方点击主要负责人签字，完成手写签字后保存
+4. 点击底部暂存按钮，确认保存成功后自动返回任务列表/首页
+5. 再次进入同一任务，确认提示恢复暂存，选择继续填写
+6. 补齐检查项并提交检查，在安全检查记录详情核对签名字段</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1. 现场信息区显示现场人员签名子表，并在其下方单独显示主要负责人签字（选填），主要负责人签字不作为子表新增行
+2. 点击暂存后保存本地草稿并自动回到任务列表/首页，不停留在执行检查页面
+3. 暂存后同一任务再次打开会提示恢复，恢复后检查项结果、异常说明、整改要求、处理情况、异常照片、现场照片、现场人员签名和主要负责人签字均保留
+4. 提交 payload 包含 principalSignature，后端上传后写入安全检查提交主表 _widget_1780728739295
+5. 提交成功后清除该任务本地草稿，再次进入同一任务不再恢复旧草稿
+6. 安全检查记录详情可查看主要负责人签字图片，现场人员签名仍来自原签名子表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核对 localStorage 草稿 key、/api/safety-check/submit 请求体、提交主表 _widget_1780728739295 及记录详情返回 principalSignatureFiles。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J120" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">集成手工</x:t>
+        </x:is>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/system-test-cases/点巡检系统测试用例.xlsx
+++ b/outputs/system-test-cases/点巡检系统测试用例.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="Rf6364159849a46a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能用例" sheetId="2" r:id="Rcc0bb9d2761441d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="百数云入口检查清单" sheetId="3" r:id="R43937c5f9323464d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API与数据校验" sheetId="4" r:id="Rfb1db86c2ea549b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与回归" sheetId="5" r:id="R26e438d5030c4819"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试数据准备" sheetId="6" r:id="R35935b8da81742b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R45be7e86a04b415a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能用例" sheetId="2" r:id="R6c3bd106b4604952"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="百数云入口检查清单" sheetId="3" r:id="R43c55cd603b541fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API与数据校验" sheetId="4" r:id="R5f186935605d4cad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与回归" sheetId="5" r:id="Re05f51b24af84144"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试数据准备" sheetId="6" r:id="R5f671c19a8f745dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2173,10 +2173,8 @@
           <x:t xml:space="preserve">危化品台账加载列表和关联选项</x:t>
         </x:is>
       </x:c>
-      <x:c r="F22" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">危化品台账、点检标准、人员、包装形式、事故类型、场地底表存在数据。</x:t>
-        </x:is>
+      <x:c r="F22" s="8" t="str">
+        <x:v>危化品台账、点检标准、人员、包装形式、事故类型、场地底表存在数据；危化品底表数据量可超过 300 条用于验证全量同步。</x:v>
       </x:c>
       <x:c r="G22" s="8" t="inlineStr">
         <x:is>
@@ -2185,12 +2183,13 @@
         </x:is>
       </x:c>
       <x:c r="H22" s="8" t="str">
-        <x:v>1. 列表展示编号、名称、状态、纳入点检、存放位置、最大存放量、包装形式、事故类型、责任人
-2. 下拉选项可搜索并能选择
-3. 存放位置下拉按场地一二级层级展示，一级可选，二级显示/保存为“一级-二级”，选项不展示场地编号</x:v>
+        <x:v>1. 页面优先通过 data_count 获取总数，并按 limit=300、skip 分页汇总危化品底表全量数据
+2. 列表展示编号、名称、状态、纳入点检、存放位置、最大存放量、包装形式、事故类型、责任人
+3. 下拉选项可搜索并能选择
+4. 存放位置下拉按场地一二级层级展示，一级可选，二级显示/保存为“一级-二级”，选项不展示场地编号</x:v>
       </x:c>
       <x:c r="I22" s="8" t="str">
-        <x:v>核对关联选项来自对应底表或接口；场地底表旧值只存二级名称或编号时仍可识别并归一显示。</x:v>
+        <x:v>核对列表总数与百数云危化品底表 data_count 一致，不只显示首批 300 条；关联选项来自对应底表或接口；场地底表旧值只存二级名称或编号时仍可识别并归一显示。</x:v>
       </x:c>
       <x:c r="J22" s="8" t="inlineStr">
         <x:is>
@@ -6229,41 +6228,24 @@
           <x:t xml:space="preserve">存在正常和异常检查提交记录；至少一条记录包含现场签名，以及异常项说明、整改要求/措施、处理情况和异常照片。</x:t>
         </x:is>
       </x:c>
-      <x:c r="G90" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 从百数云菜单进入检查记录页面
-2. 按提交编号、检查类型、检查人、区域对象搜索
-3. 按结果筛选，观察分页是否回到第 1 页
-4. 切换每页 10/20/50 条并翻页
-5. 点击详情查看明细
-6. 在详情弹窗右下角点击编辑，确认检查时间在当前详情弹窗内变成可编辑输入框
-7. 修改检查时间并在当前详情弹窗内保存
-8. 勾选一条或多条记录，在顶部菜单点击打印和导出
-9. 切换打印模板后再次批量打印/导出</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H90" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 页面右上角不显示刷新按钮，底部不显示“准备就绪”状态栏
-2. 列表默认每页 10 条，分页条展示总数、当前显示范围、页码和上一页/下一页；可切换 10/20/50 条每页
-3. 筛选条件变化后回到第 1 页；表头全选只选择当前页，跨页已勾选记录在当前筛选结果内保留
-4. 列表展示提交编号、检查类型、区域、检查人、检查时间、结果、异常数、状态；表格内容垂直居中，结果、异常数、状态、操作等短字段居中显示；行内操作只显示详情
-5. 详情弹窗右下角显示编辑按钮；点击后不打开新的页面或二级弹窗，而是在当前详情弹窗内把检查时间切换为可编辑输入框，并显示取消/保存按钮
-6. 保存后回写安全检查提交主表结束时间字段，当前详情弹窗恢复展示态，列表/详情中的检查时间刷新
-7. 打印和导出位于顶部菜单栏；勾选多条记录后可批量打印/导出，未勾选时可处理当前选中行
-8. 详情展示每项结果、异常说明、整改要求/措施、处理情况、异常照片和整改流程；异常照片以缩略图显示，不只显示文件链接，并展示现场签名图片
-9. 打印支持结果检查表和记录检查表两套模板，标题不重复“检查”，A4 页面表格宽度、元信息、签名和日期布局贴近检查表模板
-10. 明细打印模板顶部显示检查日期和检查人员签字，不显示单位名称；底部不再重复检查人员和检查日期
-11. 底部检查人员和检查日期两侧填写栏等高、横线对齐，签名图片尺寸受控，不撑高左侧栏
-12. 右侧“如不符合”列仅异常项填写存在问题和整改措施，正常项为空，不带现场照片、签字时间、异常照片或整改流程编号
-13. 检查人员取签名子表手写签名字段并显示签名图片，多个签名以“、”分隔，不取主表检查人/提交人；检查日期带出检查时间日期
-14. 导出文件可用 Excel 打开且不影响其他安全检查页面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I90" s="8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">分页仅影响列表展示；批量打印/导出按已勾选记录处理，表头全选仅选择当前页。编辑检查时间入口位于详情弹窗右下角，点击后在当前详情弹窗内联编辑，只更新提交主表 endTime，不修改检查明细、签名或隐患数据。</x:t>
-        </x:is>
+      <x:c r="G90" s="8" t="str">
+        <x:v>1. 从百数云菜单进入安全检查记录页
+2. 搜索、筛选并打开一条包含异常、异常照片和多人签字的记录详情
+3. 查看详情基础信息、签字信息和检查明细样式
+4. 点击详情右下角编辑，修改检查时间并保存
+5. 勾选多条记录后点击打印/导出</x:v>
+      </x:c>
+      <x:c r="H90" s="8" t="str">
+        <x:v>1. 列表默认每页 10 条，分页、筛选和表头全选逻辑正确
+2. 详情弹窗标题只显示检查类型，不在标题前拼提交编号；提交编号仅在基础信息中展示
+3. 详情弹窗按常规数据详情页样式分区展示基础信息、签字信息、检查明细，字段对齐清晰
+4. 检查明细不展示整改流程/隐患流程 ID 字符串，仅展示结果、异常说明、整改/处理措施、处理情况和异常照片
+5. 异常照片以缩略图展示；检查人员签字支持多人签名换行/滚动，不撑乱详情布局
+6. 编辑只开放检查时间字段，保存后列表和详情同步更新
+7. 批量打印/导出按勾选记录执行</x:v>
+      </x:c>
+      <x:c r="I90" s="8" t="str">
+        <x:v>核对提交主表检查时间字段 _widget_1776820784314 已更新；详情签名取主表签名子表手写签名字段；详情标题不包含提交编号，且不暴露 hazardId/整改流程 ID。</x:v>
       </x:c>
       <x:c r="J90" s="8" t="inlineStr">
         <x:is>
@@ -7861,10 +7843,8 @@
           <x:t xml:space="preserve">危化品数量较多时列表默认 20 条分页展示</x:t>
         </x:is>
       </x:c>
-      <x:c r="F117" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">危化品台账中准备超过 20 条危化品记录，且至少一个地点或全部地点筛选结果超过 20 条。</x:t>
-        </x:is>
+      <x:c r="F117" t="str">
+        <x:v>危化品底表存在超过 300 条数据，且前 300 条之后包含可搜索的测试记录。</x:v>
       </x:c>
       <x:c r="G117" t="inlineStr">
         <x:is>
@@ -7875,19 +7855,15 @@
 5. 执行关键字、状态或地点树筛选后再次查看分页</x:t>
         </x:is>
       </x:c>
-      <x:c r="H117" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1. 默认每页显示 20 条危化品记录，避免大量行挤满页面
-2. 分页条显示当前页、总页数和当前页范围
-3. 切换页码或每页条数后表格内容更新且布局保持清晰
-4. 搜索、状态筛选、地点树切换后自动回到第一页
-5. 导出仍按当前筛选结果全量导出，不只导出当前页</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I117" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">核对底部统计中的总数、当前筛选数、当前页范围与页面展示一致；分页不影响详情、编辑、删除和导出。</x:t>
-        </x:is>
+      <x:c r="H117" t="str">
+        <x:v>1. 初次加载后列表总数与百数云危化品底表总数一致，不受 300 条首批限制
+2. 默认每页 20 条，分页控件显示总页数和当前范围
+3. 搜索、状态筛选、地点树切换后回到第 1 页
+4. 第 300 条之后的数据可通过分页或搜索展示
+5. 导出按当前筛选结果全量导出</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>接口层核对 data_count 与按 skip 汇总后的去重条数；页面分页只影响展示，不影响全量搜索和导出。</x:v>
       </x:c>
       <x:c r="J117" t="inlineStr">
         <x:is>
@@ -9190,6 +9166,23 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>API-024</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>百数云全量取数</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>点检标准、点检报工、点检规则、安全检查模板/任务/记录、相关方培训记录等列表读取</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>当任一业务底表数据量超过 300 条时，页面或后端初始化仍需读取全量数据</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>优先调用 data_count 获取总数，再按 data 接口 limit=300、skip=0/300/600... 分页汇总并去重；data_count 不可用时才回退兼容查询接口；页面列表、筛选、任务生成、记录详情不因单次接口批次上限丢数据。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -9557,6 +9550,23 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>R-013</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>回归重点</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>列表取数逻辑变更后</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>准备或模拟超过 300 条的点检标准/安全检查提交记录/相关方培训记录，打开对应页面并触发后端初始化</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>页面总数、分页、搜索筛选和后端任务/记录计算结果均覆盖 300 条之后的数据；不再依赖 limit=1000 或接口默认返回批次。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
